--- a/hrms-api/wwwroot/Templates/employee_template.xlsx
+++ b/hrms-api/wwwroot/Templates/employee_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Documents\VsCode\hrms-api\hrms-api\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B355951-2460-42D1-A1E3-4A7E64F5FD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58437662-9856-473F-AA4C-51E288E48AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB0C57D7-EEA7-4E4B-801E-9CD0B5FFF564}"/>
   </bookViews>
@@ -47,7 +47,6 @@
     <author>tc={0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}</author>
     <author>tc={B19BC939-9062-41D8-A080-1F0317F4D29D}</author>
     <author>tc={F0E96506-AAF2-49B7-AD58-D5B640AC0623}</author>
-    <author>tc={D61BC91A-A268-4E38-B547-D8EB3E4688B8}</author>
   </authors>
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0" xr:uid="{9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}">
@@ -127,20 +126,12 @@
 </t>
       </text>
     </comment>
-    <comment ref="W2" authorId="9" shapeId="0" xr:uid="{D61BC91A-A268-4E38-B547-D8EB3E4688B8}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Payroll frequency serves as the basis for calculating government statutory deductions. </t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>LastName</t>
   </si>
@@ -206,9 +197,6 @@
   </si>
   <si>
     <t>PaidLunchBreak</t>
-  </si>
-  <si>
-    <t>PayrollFrequency</t>
   </si>
   <si>
     <t>Saturday</t>
@@ -233,24 +221,6 @@
  specific instructions. Finally, remove any extra or blank rows at the end so the system does not read unwanted entries.</t>
   </si>
   <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>Semi Montly</t>
-  </si>
-  <si>
-    <t>Monthly</t>
-  </si>
-  <si>
-    <t>1stCutoff_IsEndOfMonth</t>
-  </si>
-  <si>
-    <t>2ndCutoff_IsEndOfMonth</t>
-  </si>
-  <si>
     <t>SalaryType</t>
   </si>
   <si>
@@ -258,15 +228,6 @@
   </si>
   <si>
     <t>MONTHLY_VARIABLE</t>
-  </si>
-  <si>
-    <t>MONTHLY_FIXED</t>
-  </si>
-  <si>
-    <t>CutoffDay1</t>
-  </si>
-  <si>
-    <t>CutoffDay2</t>
   </si>
 </sst>
 </file>
@@ -696,18 +657,16 @@
 By specifying the correct salary type, the system ensures accurate payroll processing and compliance with company policies
 </text>
   </threadedComment>
-  <threadedComment ref="W2" dT="2026-02-28T00:23:30.04" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{D61BC91A-A268-4E38-B547-D8EB3E4688B8}">
-    <text xml:space="preserve">Payroll frequency serves as the basis for calculating government statutory deductions. </text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38D9F31A-E2EC-4988-BBA0-8862FC76D1CC}">
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -725,19 +684,14 @@
     <col min="20" max="20" width="20" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -760,7 +714,7 @@
       <c r="U1" s="7"/>
       <c r="V1" s="5"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -825,42 +779,27 @@
         <v>21</v>
       </c>
       <c r="V2" t="s">
-        <v>36</v>
-      </c>
-      <c r="W2" t="s">
-        <v>22</v>
-      </c>
-      <c r="X2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>34</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
+      <c r="M3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" t="s">
+      <c r="O3" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="P3" s="1">
         <v>0.5</v>
@@ -881,110 +820,21 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>37</v>
-      </c>
-      <c r="W3" t="s">
         <v>30</v>
       </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="b">
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
       <c r="V4" t="s">
-        <v>38</v>
-      </c>
-      <c r="W4" t="s">
         <v>31</v>
-      </c>
-      <c r="Y4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="V5" t="s">
-        <v>39</v>
-      </c>
-      <c r="W5" t="s">
-        <v>32</v>
-      </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>15</v>
-      </c>
-      <c r="AA5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="W6" t="s">
-        <v>33</v>
-      </c>
-      <c r="X6">
-        <v>31</v>
-      </c>
-      <c r="Y6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="W7" t="s">
-        <v>32</v>
-      </c>
-      <c r="X7">
-        <v>5</v>
-      </c>
-      <c r="Y7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>20</v>
-      </c>
-      <c r="AA7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="W8" t="s">
-        <v>32</v>
-      </c>
-      <c r="X8">
-        <v>16</v>
-      </c>
-      <c r="Y8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>31</v>
-      </c>
-      <c r="AA8" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/hrms-api/wwwroot/Templates/employee_template.xlsx
+++ b/hrms-api/wwwroot/Templates/employee_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Documents\VsCode\hrms-api\hrms-api\wwwroot\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58437662-9856-473F-AA4C-51E288E48AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0607255D-A951-43B9-9AA6-E82A6A426F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB0C57D7-EEA7-4E4B-801E-9CD0B5FFF564}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB0C57D7-EEA7-4E4B-801E-9CD0B5FFF564}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>LastName</t>
   </si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t>Fixed</t>
-  </si>
-  <si>
-    <t>Flexi</t>
   </si>
   <si>
     <t>Daysshift - 08:00-17:00</t>
@@ -224,10 +221,22 @@
     <t>SalaryType</t>
   </si>
   <si>
-    <t>DAILY</t>
-  </si>
-  <si>
-    <t>MONTHLY_VARIABLE</t>
+    <t>Hire Date</t>
+  </si>
+  <si>
+    <t>SSS</t>
+  </si>
+  <si>
+    <t>PHIC</t>
+  </si>
+  <si>
+    <t>HDMF</t>
+  </si>
+  <si>
+    <t>Daily Rate</t>
+  </si>
+  <si>
+    <t>Variable</t>
   </si>
 </sst>
 </file>
@@ -662,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38D9F31A-E2EC-4988-BBA0-8862FC76D1CC}">
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -677,21 +686,22 @@
     <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="18" width="8.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="20" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -713,8 +723,9 @@
       <c r="T1" s="7"/>
       <c r="U1" s="7"/>
       <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -779,10 +790,25 @@
         <v>21</v>
       </c>
       <c r="V2" t="s">
+        <v>28</v>
+      </c>
+      <c r="W2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" t="s">
         <v>29</v>
       </c>
+      <c r="Y2" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -793,13 +819,13 @@
         <v>23</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
         <v>24</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P3" s="1">
         <v>0.5</v>
@@ -820,21 +846,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/hrms-api/wwwroot/Templates/employee_template.xlsx
+++ b/hrms-api/wwwroot/Templates/employee_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Documents\VsCode\hrms-api\hrms-api\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0607255D-A951-43B9-9AA6-E82A6A426F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547E4621-5D0D-4EB1-9E30-C586606A8854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB0C57D7-EEA7-4E4B-801E-9CD0B5FFF564}"/>
   </bookViews>
@@ -41,6 +41,10 @@
     <author>tc={9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}</author>
     <author>tc={79FCC02C-F85F-405C-A566-509890A3EBC9}</author>
     <author>tc={06C68CE5-F9F3-46D3-97DC-8969C057FDE5}</author>
+    <author>tc={96EB2AF4-8857-453C-84CF-C7D0294A47E1}</author>
+    <author>tc={ED936B87-B4EA-49D2-9847-251F065AD106}</author>
+    <author>tc={861CEFFE-75F3-4A22-A7B0-DE08527FCA28}</author>
+    <author>tc={41A77145-9368-44AE-B73E-F2FA9D9BF935}</author>
     <author>tc={73102409-9A79-496E-AAB6-27215C458146}</author>
     <author>tc={C3B48641-F285-4034-95EA-970F81F494AD}</author>
     <author>tc={A1D30F49-4CC7-4810-8930-31A0E5E3D18D}</author>
@@ -73,15 +77,47 @@
     Enter the day name in the column, or leave it blank if not applicable </t>
       </text>
     </comment>
-    <comment ref="M2" authorId="3" shapeId="0" xr:uid="{73102409-9A79-496E-AAB6-27215C458146}">
+    <comment ref="N2" authorId="3" shapeId="0" xr:uid="{96EB2AF4-8857-453C-84CF-C7D0294A47E1}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
+    End of Month</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="4" shapeId="0" xr:uid="{ED936B87-B4EA-49D2-9847-251F065AD106}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    End of Month</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="5" shapeId="0" xr:uid="{861CEFFE-75F3-4A22-A7B0-DE08527FCA28}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    End of Month</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="6" shapeId="0" xr:uid="{41A77145-9368-44AE-B73E-F2FA9D9BF935}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    End of Month</t>
+      </text>
+    </comment>
+    <comment ref="U2" authorId="7" shapeId="0" xr:uid="{73102409-9A79-496E-AAB6-27215C458146}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     You can Enter any Time Shift name here</t>
       </text>
     </comment>
-    <comment ref="O2" authorId="4" shapeId="0" xr:uid="{C3B48641-F285-4034-95EA-970F81F494AD}">
+    <comment ref="W2" authorId="8" shapeId="0" xr:uid="{C3B48641-F285-4034-95EA-970F81F494AD}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -89,7 +125,7 @@
     Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </t>
       </text>
     </comment>
-    <comment ref="Q2" authorId="5" shapeId="0" xr:uid="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
+    <comment ref="Y2" authorId="9" shapeId="0" xr:uid="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -97,7 +133,7 @@
     Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </t>
       </text>
     </comment>
-    <comment ref="R2" authorId="6" shapeId="0" xr:uid="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
+    <comment ref="Z2" authorId="10" shapeId="0" xr:uid="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -106,7 +142,7 @@
 </t>
       </text>
     </comment>
-    <comment ref="T2" authorId="7" shapeId="0" xr:uid="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
+    <comment ref="AB2" authorId="11" shapeId="0" xr:uid="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -114,7 +150,7 @@
     This field represents the total working minutes in a day, excluding unpaid breaks. For example, 480 minutes correspond to 8 hours. If an employee is on a compressed schedule, such as 9 hours per day, you must enter the calculation (9 × 60 = 540) to reflect the correct total. </t>
       </text>
     </comment>
-    <comment ref="V2" authorId="8" shapeId="0" xr:uid="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
+    <comment ref="AD2" authorId="12" shapeId="0" xr:uid="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -131,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
   <si>
     <t>LastName</t>
   </si>
@@ -237,13 +273,46 @@
   </si>
   <si>
     <t>Variable</t>
+  </si>
+  <si>
+    <t>Cut-Off1</t>
+  </si>
+  <si>
+    <t>Cut-Off2</t>
+  </si>
+  <si>
+    <t>Cut-Off3</t>
+  </si>
+  <si>
+    <t>Cut-Off4</t>
+  </si>
+  <si>
+    <t>Semi-Monthly</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>EOM1</t>
+  </si>
+  <si>
+    <t>EOM2</t>
+  </si>
+  <si>
+    <t>EOM3</t>
+  </si>
+  <si>
+    <t>EOM4</t>
+  </si>
+  <si>
+    <t>Monthly</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +326,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -643,23 +718,35 @@
   <threadedComment ref="I2" dT="2026-02-27T23:40:49.87" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{06C68CE5-F9F3-46D3-97DC-8969C057FDE5}">
     <text xml:space="preserve">Enter the day name in the column, or leave it blank if not applicable </text>
   </threadedComment>
-  <threadedComment ref="M2" dT="2026-02-27T23:55:36.90" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{73102409-9A79-496E-AAB6-27215C458146}">
+  <threadedComment ref="N2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{96EB2AF4-8857-453C-84CF-C7D0294A47E1}">
+    <text>End of Month</text>
+  </threadedComment>
+  <threadedComment ref="P2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{ED936B87-B4EA-49D2-9847-251F065AD106}">
+    <text>End of Month</text>
+  </threadedComment>
+  <threadedComment ref="R2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{861CEFFE-75F3-4A22-A7B0-DE08527FCA28}">
+    <text>End of Month</text>
+  </threadedComment>
+  <threadedComment ref="T2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{41A77145-9368-44AE-B73E-F2FA9D9BF935}">
+    <text>End of Month</text>
+  </threadedComment>
+  <threadedComment ref="U2" dT="2026-02-27T23:55:36.90" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{73102409-9A79-496E-AAB6-27215C458146}">
     <text>You can Enter any Time Shift name here</text>
   </threadedComment>
-  <threadedComment ref="O2" dT="2026-02-27T23:59:32.14" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{C3B48641-F285-4034-95EA-970F81F494AD}">
+  <threadedComment ref="W2" dT="2026-02-27T23:59:32.14" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{C3B48641-F285-4034-95EA-970F81F494AD}">
     <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </text>
   </threadedComment>
-  <threadedComment ref="Q2" dT="2026-02-28T00:02:04.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
+  <threadedComment ref="Y2" dT="2026-02-28T00:02:04.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
     <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </text>
   </threadedComment>
-  <threadedComment ref="R2" dT="2026-02-28T00:02:10.16" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
+  <threadedComment ref="Z2" dT="2026-02-28T00:02:10.16" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
     <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. 
 </text>
   </threadedComment>
-  <threadedComment ref="T2" dT="2026-02-28T00:09:02.95" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
+  <threadedComment ref="AB2" dT="2026-02-28T00:09:02.95" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
     <text xml:space="preserve">This field represents the total working minutes in a day, excluding unpaid breaks. For example, 480 minutes correspond to 8 hours. If an employee is on a compressed schedule, such as 9 hours per day, you must enter the calculation (9 × 60 = 540) to reflect the correct total. </text>
   </threadedComment>
-  <threadedComment ref="V2" dT="2026-02-28T00:29:11.91" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
+  <threadedComment ref="AD2" dT="2026-02-28T00:29:11.91" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
     <text xml:space="preserve">The Salary Type column defines how an employee’s salary is calculated for the payroll period. It determines whether the computation is based on actual work hours or on a fixed monthly rate.
 Daily and Monthly Variable: Salary is computed based on the employee’s recorded work hours. This means pay is directly tied to attendance and the number of hours worked within the period.
 Monthly Fixed: Salary is calculated based on the employee’s fixed monthly rate. Deductions are applied for lateness, undertime (UT), and absences, but the base salary remains constant regardless of daily work hours.
@@ -671,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38D9F31A-E2EC-4988-BBA0-8862FC76D1CC}">
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -685,18 +772,27 @@
     <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.85546875" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7109375" customWidth="1"/>
+    <col min="23" max="23" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="8.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.85546875" customWidth="1"/>
+    <col min="32" max="32" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -722,10 +818,18 @@
       <c r="S1" s="7"/>
       <c r="T1" s="7"/>
       <c r="U1" s="7"/>
-      <c r="V1" s="5"/>
-      <c r="W1" s="5"/>
+      <c r="V1" s="7"/>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
+      <c r="AA1" s="7"/>
+      <c r="AB1" s="7"/>
+      <c r="AC1" s="7"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -763,52 +867,76 @@
         <v>12</v>
       </c>
       <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s">
+      <c r="V2" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="AA2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="AB2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AC2" t="s">
         <v>21</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AD2" t="s">
         <v>28</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AE2" t="s">
         <v>33</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AF2" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AG2" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AH2" t="s">
         <v>31</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AI2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -818,40 +946,124 @@
       <c r="I3" t="s">
         <v>23</v>
       </c>
-      <c r="M3" t="s">
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>15</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="s">
         <v>25</v>
       </c>
-      <c r="N3" t="s">
+      <c r="V3" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="P3" s="1">
+      <c r="X3" s="1">
         <v>0.5</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Y3" s="1">
         <v>0.54166666666666663</v>
       </c>
-      <c r="R3" s="1">
+      <c r="Z3" s="1">
         <v>0.70833333333333337</v>
       </c>
-      <c r="S3" s="4">
+      <c r="AA3" s="4">
         <v>60</v>
       </c>
-      <c r="T3" s="4">
+      <c r="AB3" s="4">
         <v>480</v>
       </c>
-      <c r="U3" t="b">
+      <c r="AC3" t="b">
         <v>1</v>
       </c>
-      <c r="V3" t="s">
+      <c r="AD3" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4">
+        <v>10</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>25</v>
+      </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5">
+        <v>7</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>14</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>21</v>
+      </c>
+      <c r="R5" t="b">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>31</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M6">
+        <v>31</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:U1"/>
+    <mergeCell ref="B1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/hrms-api/wwwroot/Templates/employee_template.xlsx
+++ b/hrms-api/wwwroot/Templates/employee_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Documents\VsCode\hrms-api\hrms-api\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{547E4621-5D0D-4EB1-9E30-C586606A8854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB31E980-C976-443A-97C4-407DFF1F46B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB0C57D7-EEA7-4E4B-801E-9CD0B5FFF564}"/>
   </bookViews>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>LastName</t>
   </si>
@@ -306,13 +306,16 @@
   </si>
   <si>
     <t>Monthly</t>
+  </si>
+  <si>
+    <t>Email</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,12 +329,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -758,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38D9F31A-E2EC-4988-BBA0-8862FC76D1CC}">
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -792,7 +789,7 @@
     <col min="32" max="32" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -829,7 +826,7 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -935,8 +932,11 @@
       <c r="AI2" t="s">
         <v>32</v>
       </c>
+      <c r="AJ2" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -998,7 +998,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="L4" t="s">
         <v>39</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="L5" t="s">
         <v>40</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="L6" t="s">
         <v>45</v>
       </c>

--- a/hrms-api/wwwroot/Templates/employee_template.xlsx
+++ b/hrms-api/wwwroot/Templates/employee_template.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Documents\VsCode\hrms-api\hrms-api\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB31E980-C976-443A-97C4-407DFF1F46B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B957B507-6E0E-4516-A937-88DE5587A032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB0C57D7-EEA7-4E4B-801E-9CD0B5FFF564}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,228 +32,109 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}</author>
-    <author>tc={79FCC02C-F85F-405C-A566-509890A3EBC9}</author>
-    <author>tc={06C68CE5-F9F3-46D3-97DC-8969C057FDE5}</author>
-    <author>tc={96EB2AF4-8857-453C-84CF-C7D0294A47E1}</author>
-    <author>tc={ED936B87-B4EA-49D2-9847-251F065AD106}</author>
-    <author>tc={861CEFFE-75F3-4A22-A7B0-DE08527FCA28}</author>
-    <author>tc={41A77145-9368-44AE-B73E-F2FA9D9BF935}</author>
-    <author>tc={73102409-9A79-496E-AAB6-27215C458146}</author>
-    <author>tc={C3B48641-F285-4034-95EA-970F81F494AD}</author>
-    <author>tc={A1D30F49-4CC7-4810-8930-31A0E5E3D18D}</author>
-    <author>tc={0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}</author>
-    <author>tc={B19BC939-9062-41D8-A080-1F0317F4D29D}</author>
-    <author>tc={F0E96506-AAF2-49B7-AD58-D5B640AC0623}</author>
-  </authors>
-  <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    This is the biometric ID that must be set on the device </t>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="1" shapeId="0" xr:uid="{79FCC02C-F85F-405C-A566-509890A3EBC9}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Enter the day name in the column, or leave it blank if not applicable </t>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="2" shapeId="0" xr:uid="{06C68CE5-F9F3-46D3-97DC-8969C057FDE5}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Enter the day name in the column, or leave it blank if not applicable </t>
-      </text>
-    </comment>
-    <comment ref="N2" authorId="3" shapeId="0" xr:uid="{96EB2AF4-8857-453C-84CF-C7D0294A47E1}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    End of Month</t>
-      </text>
-    </comment>
-    <comment ref="P2" authorId="4" shapeId="0" xr:uid="{ED936B87-B4EA-49D2-9847-251F065AD106}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    End of Month</t>
-      </text>
-    </comment>
-    <comment ref="R2" authorId="5" shapeId="0" xr:uid="{861CEFFE-75F3-4A22-A7B0-DE08527FCA28}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    End of Month</t>
-      </text>
-    </comment>
-    <comment ref="T2" authorId="6" shapeId="0" xr:uid="{41A77145-9368-44AE-B73E-F2FA9D9BF935}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    End of Month</t>
-      </text>
-    </comment>
-    <comment ref="U2" authorId="7" shapeId="0" xr:uid="{73102409-9A79-496E-AAB6-27215C458146}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    You can Enter any Time Shift name here</t>
-      </text>
-    </comment>
-    <comment ref="W2" authorId="8" shapeId="0" xr:uid="{C3B48641-F285-4034-95EA-970F81F494AD}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </t>
-      </text>
-    </comment>
-    <comment ref="Y2" authorId="9" shapeId="0" xr:uid="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </t>
-      </text>
-    </comment>
-    <comment ref="Z2" authorId="10" shapeId="0" xr:uid="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. 
-</t>
-      </text>
-    </comment>
-    <comment ref="AB2" authorId="11" shapeId="0" xr:uid="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    This field represents the total working minutes in a day, excluding unpaid breaks. For example, 480 minutes correspond to 8 hours. If an employee is on a compressed schedule, such as 9 hours per day, you must enter the calculation (9 × 60 = 540) to reflect the correct total. </t>
-      </text>
-    </comment>
-    <comment ref="AD2" authorId="12" shapeId="0" xr:uid="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    The Salary Type column defines how an employee’s salary is calculated for the payroll period. It determines whether the computation is based on actual work hours or on a fixed monthly rate.
-Daily and Monthly Variable: Salary is computed based on the employee’s recorded work hours. This means pay is directly tied to attendance and the number of hours worked within the period.
-Monthly Fixed: Salary is calculated based on the employee’s fixed monthly rate. Deductions are applied for lateness, undertime (UT), and absences, but the base salary remains constant regardless of daily work hours.
-By specifying the correct salary type, the system ensures accurate payroll processing and compliance with company policies
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>MiddleName</t>
-  </si>
-  <si>
     <t>Instructions:</t>
-  </si>
-  <si>
-    <t>BioId</t>
-  </si>
-  <si>
-    <t>Branch Code</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>Suffix</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Rest Day 1</t>
-  </si>
-  <si>
-    <t>Rest Day 2</t>
-  </si>
-  <si>
-    <t>Department Name</t>
-  </si>
-  <si>
-    <t>Client Name</t>
-  </si>
-  <si>
-    <t>Payroll Group</t>
-  </si>
-  <si>
-    <t>Shift Name</t>
-  </si>
-  <si>
-    <t>Shift Type</t>
-  </si>
-  <si>
-    <t>AMIN</t>
-  </si>
-  <si>
-    <t>AM Out</t>
-  </si>
-  <si>
-    <t>PM In</t>
-  </si>
-  <si>
-    <t>PM OUT</t>
-  </si>
-  <si>
-    <t>Break Duration</t>
-  </si>
-  <si>
-    <t>Max Working Minutes</t>
-  </si>
-  <si>
-    <t>PaidLunchBreak</t>
-  </si>
-  <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>Fixed</t>
-  </si>
-  <si>
-    <t>Daysshift - 08:00-17:00</t>
-  </si>
-  <si>
-    <t>8:00:00AM</t>
   </si>
   <si>
     <t>Sample data are provided for each column. Before filling out this template, copy the data starting from the third row down to the last row of your dataset to ensure that all formulas and validations are carried over. I have also added comments in certain columns with
  specific instructions. Finally, remove any extra or blank rows at the end so the system does not read unwanted entries.</t>
   </si>
   <si>
+    <t>BioId</t>
+  </si>
+  <si>
+    <t>Branch Code</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>MiddleName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Suffix</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Rest Day 1</t>
+  </si>
+  <si>
+    <t>Rest Day 2</t>
+  </si>
+  <si>
+    <t>Department Name</t>
+  </si>
+  <si>
+    <t>Client Name</t>
+  </si>
+  <si>
+    <t>Payroll Group</t>
+  </si>
+  <si>
+    <t>Cut-Off 1</t>
+  </si>
+  <si>
+    <t>EOM 1</t>
+  </si>
+  <si>
+    <t>Cut-Off 2</t>
+  </si>
+  <si>
+    <t>EOM 2</t>
+  </si>
+  <si>
+    <t>Cut-Off 3</t>
+  </si>
+  <si>
+    <t>EOM 3</t>
+  </si>
+  <si>
+    <t>Cut-Off 4</t>
+  </si>
+  <si>
+    <t>EOM 4</t>
+  </si>
+  <si>
+    <t>Shift Name</t>
+  </si>
+  <si>
+    <t>Shift Type</t>
+  </si>
+  <si>
+    <t>AMIN</t>
+  </si>
+  <si>
+    <t>AM Out</t>
+  </si>
+  <si>
+    <t>PM In</t>
+  </si>
+  <si>
+    <t>PM OUT</t>
+  </si>
+  <si>
+    <t>Break Duration</t>
+  </si>
+  <si>
+    <t>Max Working Minutes</t>
+  </si>
+  <si>
+    <t>PaidLunchBreak</t>
+  </si>
+  <si>
     <t>SalaryType</t>
   </si>
   <si>
+    <t>Daily Rate</t>
+  </si>
+  <si>
     <t>Hire Date</t>
   </si>
   <si>
@@ -269,46 +147,34 @@
     <t>HDMF</t>
   </si>
   <si>
-    <t>Daily Rate</t>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Semi-Monthly</t>
+  </si>
+  <si>
+    <t>Daysshift - 08:00-17:00</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>8:00:00AM</t>
   </si>
   <si>
     <t>Variable</t>
   </si>
   <si>
-    <t>Cut-Off1</t>
-  </si>
-  <si>
-    <t>Cut-Off2</t>
-  </si>
-  <si>
-    <t>Cut-Off3</t>
-  </si>
-  <si>
-    <t>Cut-Off4</t>
-  </si>
-  <si>
-    <t>Semi-Monthly</t>
-  </si>
-  <si>
     <t>Weekly</t>
   </si>
   <si>
-    <t>EOM1</t>
-  </si>
-  <si>
-    <t>EOM2</t>
-  </si>
-  <si>
-    <t>EOM3</t>
-  </si>
-  <si>
-    <t>EOM4</t>
-  </si>
-  <si>
     <t>Monthly</t>
-  </si>
-  <si>
-    <t>Email</t>
   </si>
 </sst>
 </file>
@@ -320,14 +186,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -353,16 +219,16 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -381,12 +247,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="jhon cee" id="{178AE33B-3851-45CE-B93D-1C219421A458}" userId="fc318abad359ea5a" providerId="Windows Live"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,7 +292,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -465,26 +325,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -517,23 +360,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -696,105 +522,52 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2026-02-27T23:33:46.22" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}">
-    <text xml:space="preserve">This is the biometric ID that must be set on the device </text>
-  </threadedComment>
-  <threadedComment ref="H2" dT="2026-02-27T23:40:49.87" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{79FCC02C-F85F-405C-A566-509890A3EBC9}">
-    <text xml:space="preserve">Enter the day name in the column, or leave it blank if not applicable </text>
-  </threadedComment>
-  <threadedComment ref="I2" dT="2026-02-27T23:40:49.87" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{06C68CE5-F9F3-46D3-97DC-8969C057FDE5}">
-    <text xml:space="preserve">Enter the day name in the column, or leave it blank if not applicable </text>
-  </threadedComment>
-  <threadedComment ref="N2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{96EB2AF4-8857-453C-84CF-C7D0294A47E1}">
-    <text>End of Month</text>
-  </threadedComment>
-  <threadedComment ref="P2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{ED936B87-B4EA-49D2-9847-251F065AD106}">
-    <text>End of Month</text>
-  </threadedComment>
-  <threadedComment ref="R2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{861CEFFE-75F3-4A22-A7B0-DE08527FCA28}">
-    <text>End of Month</text>
-  </threadedComment>
-  <threadedComment ref="T2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{41A77145-9368-44AE-B73E-F2FA9D9BF935}">
-    <text>End of Month</text>
-  </threadedComment>
-  <threadedComment ref="U2" dT="2026-02-27T23:55:36.90" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{73102409-9A79-496E-AAB6-27215C458146}">
-    <text>You can Enter any Time Shift name here</text>
-  </threadedComment>
-  <threadedComment ref="W2" dT="2026-02-27T23:59:32.14" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{C3B48641-F285-4034-95EA-970F81F494AD}">
-    <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </text>
-  </threadedComment>
-  <threadedComment ref="Y2" dT="2026-02-28T00:02:04.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
-    <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </text>
-  </threadedComment>
-  <threadedComment ref="Z2" dT="2026-02-28T00:02:10.16" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
-    <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. 
-</text>
-  </threadedComment>
-  <threadedComment ref="AB2" dT="2026-02-28T00:09:02.95" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
-    <text xml:space="preserve">This field represents the total working minutes in a day, excluding unpaid breaks. For example, 480 minutes correspond to 8 hours. If an employee is on a compressed schedule, such as 9 hours per day, you must enter the calculation (9 × 60 = 540) to reflect the correct total. </text>
-  </threadedComment>
-  <threadedComment ref="AD2" dT="2026-02-28T00:29:11.91" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
-    <text xml:space="preserve">The Salary Type column defines how an employee’s salary is calculated for the payroll period. It determines whether the computation is based on actual work hours or on a fixed monthly rate.
-Daily and Monthly Variable: Salary is computed based on the employee’s recorded work hours. This means pay is directly tied to attendance and the number of hours worked within the period.
-Monthly Fixed: Salary is calculated based on the employee’s fixed monthly rate. Deductions are applied for lateness, undertime (UT), and absences, but the base salary remains constant regardless of daily work hours.
-By specifying the correct salary type, the system ensures accurate payroll processing and compliance with company policies
-</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38D9F31A-E2EC-4988-BBA0-8862FC76D1CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AJ6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="8.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.85546875" customWidth="1"/>
-    <col min="32" max="32" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.875" style="1" customWidth="1"/>
+    <col min="24" max="26" width="8.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>2</v>
+    <row r="1" spans="1:36" ht="39" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -826,128 +599,128 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
       <c r="E2" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S2" t="s">
+        <v>20</v>
+      </c>
+      <c r="T2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" t="s">
+        <v>23</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH2" t="s">
         <v>35</v>
       </c>
-      <c r="N2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="AI2" t="s">
         <v>36</v>
       </c>
-      <c r="P2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="AJ2" t="s">
         <v>37</v>
       </c>
-      <c r="R2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V2" t="s">
-        <v>14</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>46</v>
-      </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -968,39 +741,39 @@
         <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="V3" t="s">
-        <v>24</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X3" s="1">
+        <v>42</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" s="6">
         <v>0.5</v>
       </c>
-      <c r="Y3" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="Z3" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="AA3" s="4">
+      <c r="Y3" s="6">
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="Z3" s="6">
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="AA3" s="2">
         <v>60</v>
       </c>
-      <c r="AB3" s="4">
+      <c r="AB3" s="2">
         <v>480</v>
       </c>
       <c r="AC3" t="b">
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.15">
       <c r="L4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1021,9 +794,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.15">
       <c r="L5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -1050,9 +823,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
       <c r="L6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M6">
         <v>31</v>
@@ -1066,6 +839,5 @@
     <mergeCell ref="B1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/hrms-api/wwwroot/Templates/employee_template.xlsx
+++ b/hrms-api/wwwroot/Templates/employee_template.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Documents\VsCode\hrms-api\hrms-api\wwwroot\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B957B507-6E0E-4516-A937-88DE5587A032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB31E980-C976-443A-97C4-407DFF1F46B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB0C57D7-EEA7-4E4B-801E-9CD0B5FFF564}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -32,149 +35,280 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}</author>
+    <author>tc={79FCC02C-F85F-405C-A566-509890A3EBC9}</author>
+    <author>tc={06C68CE5-F9F3-46D3-97DC-8969C057FDE5}</author>
+    <author>tc={96EB2AF4-8857-453C-84CF-C7D0294A47E1}</author>
+    <author>tc={ED936B87-B4EA-49D2-9847-251F065AD106}</author>
+    <author>tc={861CEFFE-75F3-4A22-A7B0-DE08527FCA28}</author>
+    <author>tc={41A77145-9368-44AE-B73E-F2FA9D9BF935}</author>
+    <author>tc={73102409-9A79-496E-AAB6-27215C458146}</author>
+    <author>tc={C3B48641-F285-4034-95EA-970F81F494AD}</author>
+    <author>tc={A1D30F49-4CC7-4810-8930-31A0E5E3D18D}</author>
+    <author>tc={0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}</author>
+    <author>tc={B19BC939-9062-41D8-A080-1F0317F4D29D}</author>
+    <author>tc={F0E96506-AAF2-49B7-AD58-D5B640AC0623}</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This is the biometric ID that must be set on the device </t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="1" shapeId="0" xr:uid="{79FCC02C-F85F-405C-A566-509890A3EBC9}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Enter the day name in the column, or leave it blank if not applicable </t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="2" shapeId="0" xr:uid="{06C68CE5-F9F3-46D3-97DC-8969C057FDE5}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Enter the day name in the column, or leave it blank if not applicable </t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="3" shapeId="0" xr:uid="{96EB2AF4-8857-453C-84CF-C7D0294A47E1}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    End of Month</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="4" shapeId="0" xr:uid="{ED936B87-B4EA-49D2-9847-251F065AD106}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    End of Month</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="5" shapeId="0" xr:uid="{861CEFFE-75F3-4A22-A7B0-DE08527FCA28}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    End of Month</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="6" shapeId="0" xr:uid="{41A77145-9368-44AE-B73E-F2FA9D9BF935}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    End of Month</t>
+      </text>
+    </comment>
+    <comment ref="U2" authorId="7" shapeId="0" xr:uid="{73102409-9A79-496E-AAB6-27215C458146}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    You can Enter any Time Shift name here</t>
+      </text>
+    </comment>
+    <comment ref="W2" authorId="8" shapeId="0" xr:uid="{C3B48641-F285-4034-95EA-970F81F494AD}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </t>
+      </text>
+    </comment>
+    <comment ref="Y2" authorId="9" shapeId="0" xr:uid="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </t>
+      </text>
+    </comment>
+    <comment ref="Z2" authorId="10" shapeId="0" xr:uid="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. 
+</t>
+      </text>
+    </comment>
+    <comment ref="AB2" authorId="11" shapeId="0" xr:uid="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    This field represents the total working minutes in a day, excluding unpaid breaks. For example, 480 minutes correspond to 8 hours. If an employee is on a compressed schedule, such as 9 hours per day, you must enter the calculation (9 × 60 = 540) to reflect the correct total. </t>
+      </text>
+    </comment>
+    <comment ref="AD2" authorId="12" shapeId="0" xr:uid="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The Salary Type column defines how an employee’s salary is calculated for the payroll period. It determines whether the computation is based on actual work hours or on a fixed monthly rate.
+Daily and Monthly Variable: Salary is computed based on the employee’s recorded work hours. This means pay is directly tied to attendance and the number of hours worked within the period.
+Monthly Fixed: Salary is calculated based on the employee’s fixed monthly rate. Deductions are applied for lateness, undertime (UT), and absences, but the base salary remains constant regardless of daily work hours.
+By specifying the correct salary type, the system ensures accurate payroll processing and compliance with company policies
+</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>MiddleName</t>
+  </si>
+  <si>
     <t>Instructions:</t>
+  </si>
+  <si>
+    <t>BioId</t>
+  </si>
+  <si>
+    <t>Branch Code</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>Suffix</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Rest Day 1</t>
+  </si>
+  <si>
+    <t>Rest Day 2</t>
+  </si>
+  <si>
+    <t>Department Name</t>
+  </si>
+  <si>
+    <t>Client Name</t>
+  </si>
+  <si>
+    <t>Payroll Group</t>
+  </si>
+  <si>
+    <t>Shift Name</t>
+  </si>
+  <si>
+    <t>Shift Type</t>
+  </si>
+  <si>
+    <t>AMIN</t>
+  </si>
+  <si>
+    <t>AM Out</t>
+  </si>
+  <si>
+    <t>PM In</t>
+  </si>
+  <si>
+    <t>PM OUT</t>
+  </si>
+  <si>
+    <t>Break Duration</t>
+  </si>
+  <si>
+    <t>Max Working Minutes</t>
+  </si>
+  <si>
+    <t>PaidLunchBreak</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>Daysshift - 08:00-17:00</t>
+  </si>
+  <si>
+    <t>8:00:00AM</t>
   </si>
   <si>
     <t>Sample data are provided for each column. Before filling out this template, copy the data starting from the third row down to the last row of your dataset to ensure that all formulas and validations are carried over. I have also added comments in certain columns with
  specific instructions. Finally, remove any extra or blank rows at the end so the system does not read unwanted entries.</t>
   </si>
   <si>
-    <t>BioId</t>
-  </si>
-  <si>
-    <t>Branch Code</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>MiddleName</t>
-  </si>
-  <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>Suffix</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Rest Day 1</t>
-  </si>
-  <si>
-    <t>Rest Day 2</t>
-  </si>
-  <si>
-    <t>Department Name</t>
-  </si>
-  <si>
-    <t>Client Name</t>
-  </si>
-  <si>
-    <t>Payroll Group</t>
-  </si>
-  <si>
-    <t>Cut-Off 1</t>
-  </si>
-  <si>
-    <t>EOM 1</t>
-  </si>
-  <si>
-    <t>Cut-Off 2</t>
-  </si>
-  <si>
-    <t>EOM 2</t>
-  </si>
-  <si>
-    <t>Cut-Off 3</t>
-  </si>
-  <si>
-    <t>EOM 3</t>
-  </si>
-  <si>
-    <t>Cut-Off 4</t>
-  </si>
-  <si>
-    <t>EOM 4</t>
-  </si>
-  <si>
-    <t>Shift Name</t>
-  </si>
-  <si>
-    <t>Shift Type</t>
-  </si>
-  <si>
-    <t>AMIN</t>
-  </si>
-  <si>
-    <t>AM Out</t>
-  </si>
-  <si>
-    <t>PM In</t>
-  </si>
-  <si>
-    <t>PM OUT</t>
-  </si>
-  <si>
-    <t>Break Duration</t>
-  </si>
-  <si>
-    <t>Max Working Minutes</t>
-  </si>
-  <si>
-    <t>PaidLunchBreak</t>
-  </si>
-  <si>
     <t>SalaryType</t>
   </si>
   <si>
+    <t>Hire Date</t>
+  </si>
+  <si>
+    <t>SSS</t>
+  </si>
+  <si>
+    <t>PHIC</t>
+  </si>
+  <si>
+    <t>HDMF</t>
+  </si>
+  <si>
     <t>Daily Rate</t>
   </si>
   <si>
-    <t>Hire Date</t>
-  </si>
-  <si>
-    <t>SSS</t>
-  </si>
-  <si>
-    <t>PHIC</t>
-  </si>
-  <si>
-    <t>HDMF</t>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Cut-Off1</t>
+  </si>
+  <si>
+    <t>Cut-Off2</t>
+  </si>
+  <si>
+    <t>Cut-Off3</t>
+  </si>
+  <si>
+    <t>Cut-Off4</t>
+  </si>
+  <si>
+    <t>Semi-Monthly</t>
+  </si>
+  <si>
+    <t>Weekly</t>
+  </si>
+  <si>
+    <t>EOM1</t>
+  </si>
+  <si>
+    <t>EOM2</t>
+  </si>
+  <si>
+    <t>EOM3</t>
+  </si>
+  <si>
+    <t>EOM4</t>
+  </si>
+  <si>
+    <t>Monthly</t>
   </si>
   <si>
     <t>Email</t>
-  </si>
-  <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>Semi-Monthly</t>
-  </si>
-  <si>
-    <t>Daysshift - 08:00-17:00</t>
-  </si>
-  <si>
-    <t>Fixed</t>
-  </si>
-  <si>
-    <t>8:00:00AM</t>
-  </si>
-  <si>
-    <t>Variable</t>
-  </si>
-  <si>
-    <t>Weekly</t>
-  </si>
-  <si>
-    <t>Monthly</t>
   </si>
 </sst>
 </file>
@@ -186,14 +320,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -219,16 +353,16 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -247,6 +381,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="jhon cee" id="{178AE33B-3851-45CE-B93D-1C219421A458}" userId="fc318abad359ea5a" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -292,7 +432,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -325,9 +465,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -360,6 +517,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -522,52 +696,105 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A2" dT="2026-02-27T23:33:46.22" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}">
+    <text xml:space="preserve">This is the biometric ID that must be set on the device </text>
+  </threadedComment>
+  <threadedComment ref="H2" dT="2026-02-27T23:40:49.87" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{79FCC02C-F85F-405C-A566-509890A3EBC9}">
+    <text xml:space="preserve">Enter the day name in the column, or leave it blank if not applicable </text>
+  </threadedComment>
+  <threadedComment ref="I2" dT="2026-02-27T23:40:49.87" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{06C68CE5-F9F3-46D3-97DC-8969C057FDE5}">
+    <text xml:space="preserve">Enter the day name in the column, or leave it blank if not applicable </text>
+  </threadedComment>
+  <threadedComment ref="N2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{96EB2AF4-8857-453C-84CF-C7D0294A47E1}">
+    <text>End of Month</text>
+  </threadedComment>
+  <threadedComment ref="P2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{ED936B87-B4EA-49D2-9847-251F065AD106}">
+    <text>End of Month</text>
+  </threadedComment>
+  <threadedComment ref="R2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{861CEFFE-75F3-4A22-A7B0-DE08527FCA28}">
+    <text>End of Month</text>
+  </threadedComment>
+  <threadedComment ref="T2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{41A77145-9368-44AE-B73E-F2FA9D9BF935}">
+    <text>End of Month</text>
+  </threadedComment>
+  <threadedComment ref="U2" dT="2026-02-27T23:55:36.90" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{73102409-9A79-496E-AAB6-27215C458146}">
+    <text>You can Enter any Time Shift name here</text>
+  </threadedComment>
+  <threadedComment ref="W2" dT="2026-02-27T23:59:32.14" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{C3B48641-F285-4034-95EA-970F81F494AD}">
+    <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </text>
+  </threadedComment>
+  <threadedComment ref="Y2" dT="2026-02-28T00:02:04.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
+    <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </text>
+  </threadedComment>
+  <threadedComment ref="Z2" dT="2026-02-28T00:02:10.16" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
+    <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. 
+</text>
+  </threadedComment>
+  <threadedComment ref="AB2" dT="2026-02-28T00:09:02.95" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
+    <text xml:space="preserve">This field represents the total working minutes in a day, excluding unpaid breaks. For example, 480 minutes correspond to 8 hours. If an employee is on a compressed schedule, such as 9 hours per day, you must enter the calculation (9 × 60 = 540) to reflect the correct total. </text>
+  </threadedComment>
+  <threadedComment ref="AD2" dT="2026-02-28T00:29:11.91" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
+    <text xml:space="preserve">The Salary Type column defines how an employee’s salary is calculated for the payroll period. It determines whether the computation is based on actual work hours or on a fixed monthly rate.
+Daily and Monthly Variable: Salary is computed based on the employee’s recorded work hours. This means pay is directly tied to attendance and the number of hours worked within the period.
+Monthly Fixed: Salary is calculated based on the employee’s fixed monthly rate. Deductions are applied for lateness, undertime (UT), and absences, but the base salary remains constant regardless of daily work hours.
+By specifying the correct salary type, the system ensures accurate payroll processing and compliance with company policies
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38D9F31A-E2EC-4988-BBA0-8862FC76D1CC}">
   <dimension ref="A1:AJ6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.25" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.875" style="1" customWidth="1"/>
-    <col min="24" max="26" width="8.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="3.875" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.7109375" customWidth="1"/>
+    <col min="23" max="23" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="8.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.85546875" customWidth="1"/>
+    <col min="32" max="32" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="39" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
+    <row r="1" spans="1:36" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -599,128 +826,128 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>9</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>10</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" t="s">
+      <c r="V2" t="s">
         <v>14</v>
       </c>
-      <c r="N2" t="s">
+      <c r="W2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" t="s">
+      <c r="X2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="R2" t="s">
+      <c r="AA2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="T2" t="s">
+      <c r="AC2" t="s">
         <v>21</v>
       </c>
-      <c r="U2" t="s">
-        <v>22</v>
-      </c>
-      <c r="V2" t="s">
-        <v>23</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AD2" t="s">
         <v>28</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AE2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF2" t="s">
         <v>29</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AG2" t="s">
         <v>30</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AH2" t="s">
         <v>31</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AI2" t="s">
         <v>32</v>
       </c>
-      <c r="AF2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>36</v>
-      </c>
       <c r="AJ2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
         <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>40</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -741,39 +968,39 @@
         <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="V3" t="s">
-        <v>42</v>
-      </c>
-      <c r="W3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" s="6">
+        <v>24</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="X3" s="1">
         <v>0.5</v>
       </c>
-      <c r="Y3" s="6">
-        <v>0.54166666666666696</v>
-      </c>
-      <c r="Z3" s="6">
-        <v>0.70833333333333304</v>
-      </c>
-      <c r="AA3" s="2">
+      <c r="Y3" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="AA3" s="4">
         <v>60</v>
       </c>
-      <c r="AB3" s="2">
+      <c r="AB3" s="4">
         <v>480</v>
       </c>
       <c r="AC3" t="b">
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="L4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -794,9 +1021,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="L5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -823,9 +1050,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="L6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M6">
         <v>31</v>
@@ -839,5 +1066,6 @@
     <mergeCell ref="B1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/hrms-api/wwwroot/Templates/employee_template.xlsx
+++ b/hrms-api/wwwroot/Templates/employee_template.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HII admin\Documents\VsCode\hrms-api\hrms-api\wwwroot\Templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB31E980-C976-443A-97C4-407DFF1F46B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CB0C57D7-EEA7-4E4B-801E-9CD0B5FFF564}"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +27,7 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}</author>
     <author>tc={79FCC02C-F85F-405C-A566-509890A3EBC9}</author>
@@ -53,106 +44,196 @@
     <author>tc={F0E96506-AAF2-49B7-AD58-D5B640AC0623}</author>
   </authors>
   <commentList>
-    <comment ref="A2" authorId="0" shapeId="0" xr:uid="{9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}">
+    <comment ref="A2" authorId="0">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     This is the biometric ID that must be set on the device </t>
+        </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="1" shapeId="0" xr:uid="{79FCC02C-F85F-405C-A566-509890A3EBC9}">
+    <comment ref="H2" authorId="1">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Enter the day name in the column, or leave it blank if not applicable </t>
+        </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="2" shapeId="0" xr:uid="{06C68CE5-F9F3-46D3-97DC-8969C057FDE5}">
+    <comment ref="I2" authorId="2">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Enter the day name in the column, or leave it blank if not applicable </t>
+        </r>
       </text>
     </comment>
-    <comment ref="N2" authorId="3" shapeId="0" xr:uid="{96EB2AF4-8857-453C-84CF-C7D0294A47E1}">
+    <comment ref="N2" authorId="3">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     End of Month</t>
+        </r>
       </text>
     </comment>
-    <comment ref="P2" authorId="4" shapeId="0" xr:uid="{ED936B87-B4EA-49D2-9847-251F065AD106}">
+    <comment ref="P2" authorId="4">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     End of Month</t>
+        </r>
       </text>
     </comment>
-    <comment ref="R2" authorId="5" shapeId="0" xr:uid="{861CEFFE-75F3-4A22-A7B0-DE08527FCA28}">
+    <comment ref="R2" authorId="5">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     End of Month</t>
+        </r>
       </text>
     </comment>
-    <comment ref="T2" authorId="6" shapeId="0" xr:uid="{41A77145-9368-44AE-B73E-F2FA9D9BF935}">
+    <comment ref="T2" authorId="6">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     End of Month</t>
+        </r>
       </text>
     </comment>
-    <comment ref="U2" authorId="7" shapeId="0" xr:uid="{73102409-9A79-496E-AAB6-27215C458146}">
+    <comment ref="U2" authorId="7">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     You can Enter any Time Shift name here</t>
+        </r>
       </text>
     </comment>
-    <comment ref="W2" authorId="8" shapeId="0" xr:uid="{C3B48641-F285-4034-95EA-970F81F494AD}">
+    <comment ref="W2" authorId="8">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </t>
+        </r>
       </text>
     </comment>
-    <comment ref="Y2" authorId="9" shapeId="0" xr:uid="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
+    <comment ref="Y2" authorId="9">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </t>
+        </r>
       </text>
     </comment>
-    <comment ref="Z2" authorId="10" shapeId="0" xr:uid="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
+    <comment ref="Z2" authorId="10">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. 
 </t>
+        </r>
       </text>
     </comment>
-    <comment ref="AB2" authorId="11" shapeId="0" xr:uid="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
+    <comment ref="AB2" authorId="11">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     This field represents the total working minutes in a day, excluding unpaid breaks. For example, 480 minutes correspond to 8 hours. If an employee is on a compressed schedule, such as 9 hours per day, you must enter the calculation (9 × 60 = 540) to reflect the correct total. </t>
+        </r>
       </text>
     </comment>
-    <comment ref="AD2" authorId="12" shapeId="0" xr:uid="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
+    <comment ref="AD2" authorId="12">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="SimSun"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     The Salary Type column defines how an employee’s salary is calculated for the payroll period. It determines whether the computation is based on actual work hours or on a fixed monthly rate.
@@ -160,6 +241,7 @@
 Monthly Fixed: Salary is calculated based on the employee’s fixed monthly rate. Deductions are applied for lateness, undertime (UT), and absences, but the base salary remains constant regardless of daily work hours.
 By specifying the correct salary type, the system ensures accurate payroll processing and compliance with company policies
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -169,94 +251,106 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
-    <t>LastName</t>
-  </si>
-  <si>
-    <t>MiddleName</t>
-  </si>
-  <si>
     <t>Instructions:</t>
-  </si>
-  <si>
-    <t>BioId</t>
-  </si>
-  <si>
-    <t>Branch Code</t>
-  </si>
-  <si>
-    <t>FirstName</t>
-  </si>
-  <si>
-    <t>Suffix</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>Rest Day 1</t>
-  </si>
-  <si>
-    <t>Rest Day 2</t>
-  </si>
-  <si>
-    <t>Department Name</t>
-  </si>
-  <si>
-    <t>Client Name</t>
-  </si>
-  <si>
-    <t>Payroll Group</t>
-  </si>
-  <si>
-    <t>Shift Name</t>
-  </si>
-  <si>
-    <t>Shift Type</t>
-  </si>
-  <si>
-    <t>AMIN</t>
-  </si>
-  <si>
-    <t>AM Out</t>
-  </si>
-  <si>
-    <t>PM In</t>
-  </si>
-  <si>
-    <t>PM OUT</t>
-  </si>
-  <si>
-    <t>Break Duration</t>
-  </si>
-  <si>
-    <t>Max Working Minutes</t>
-  </si>
-  <si>
-    <t>PaidLunchBreak</t>
-  </si>
-  <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>Fixed</t>
-  </si>
-  <si>
-    <t>Daysshift - 08:00-17:00</t>
-  </si>
-  <si>
-    <t>8:00:00AM</t>
   </si>
   <si>
     <t>Sample data are provided for each column. Before filling out this template, copy the data starting from the third row down to the last row of your dataset to ensure that all formulas and validations are carried over. I have also added comments in certain columns with
  specific instructions. Finally, remove any extra or blank rows at the end so the system does not read unwanted entries.</t>
   </si>
   <si>
+    <t>BioId</t>
+  </si>
+  <si>
+    <t>Branch Code</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>MiddleName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>Suffix</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Rest Day 1</t>
+  </si>
+  <si>
+    <t>Rest Day 2</t>
+  </si>
+  <si>
+    <t>Department Name</t>
+  </si>
+  <si>
+    <t>Client Name</t>
+  </si>
+  <si>
+    <t>Payroll Group</t>
+  </si>
+  <si>
+    <t>Cut-Off 1</t>
+  </si>
+  <si>
+    <t>EOM 1</t>
+  </si>
+  <si>
+    <t>Cut-Off 2</t>
+  </si>
+  <si>
+    <t>EOM 2</t>
+  </si>
+  <si>
+    <t>Cut-Off 3</t>
+  </si>
+  <si>
+    <t>EOM 3</t>
+  </si>
+  <si>
+    <t>Cut-Off 4</t>
+  </si>
+  <si>
+    <t>EOM 4</t>
+  </si>
+  <si>
+    <t>Shift Name</t>
+  </si>
+  <si>
+    <t>Shift Type</t>
+  </si>
+  <si>
+    <t>AMIN</t>
+  </si>
+  <si>
+    <t>AM Out</t>
+  </si>
+  <si>
+    <t>PM In</t>
+  </si>
+  <si>
+    <t>PM OUT</t>
+  </si>
+  <si>
+    <t>Break Duration</t>
+  </si>
+  <si>
+    <t>Max Working Minutes</t>
+  </si>
+  <si>
+    <t>PaidLunchBreak</t>
+  </si>
+  <si>
     <t>SalaryType</t>
   </si>
   <si>
+    <t>Daily Rate</t>
+  </si>
+  <si>
     <t>Hire Date</t>
   </si>
   <si>
@@ -269,77 +363,413 @@
     <t>HDMF</t>
   </si>
   <si>
-    <t>Daily Rate</t>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Semi-Monthly</t>
+  </si>
+  <si>
+    <t>Daysshift - 08:00-17:00</t>
+  </si>
+  <si>
+    <t>Fixed</t>
+  </si>
+  <si>
+    <t>8:00:00AM</t>
   </si>
   <si>
     <t>Variable</t>
   </si>
   <si>
-    <t>Cut-Off1</t>
-  </si>
-  <si>
-    <t>Cut-Off2</t>
-  </si>
-  <si>
-    <t>Cut-Off3</t>
-  </si>
-  <si>
-    <t>Cut-Off4</t>
-  </si>
-  <si>
-    <t>Semi-Monthly</t>
-  </si>
-  <si>
     <t>Weekly</t>
   </si>
   <si>
-    <t>EOM1</t>
-  </si>
-  <si>
-    <t>EOM2</t>
-  </si>
-  <si>
-    <t>EOM3</t>
-  </si>
-  <si>
-    <t>EOM4</t>
-  </si>
-  <si>
     <t>Monthly</t>
-  </si>
-  <si>
-    <t>Email</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -347,46 +777,323 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="35" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="jhon cee" id="{178AE33B-3851-45CE-B93D-1C219421A458}" userId="fc318abad359ea5a" providerId="Windows Live"/>
-</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,7 +1139,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -465,26 +1172,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -517,23 +1207,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -695,259 +1368,204 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A2" dT="2026-02-27T23:33:46.22" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{9BFC5F6E-C6A0-42C0-B8AB-F1F3D1249D2B}">
-    <text xml:space="preserve">This is the biometric ID that must be set on the device </text>
-  </threadedComment>
-  <threadedComment ref="H2" dT="2026-02-27T23:40:49.87" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{79FCC02C-F85F-405C-A566-509890A3EBC9}">
-    <text xml:space="preserve">Enter the day name in the column, or leave it blank if not applicable </text>
-  </threadedComment>
-  <threadedComment ref="I2" dT="2026-02-27T23:40:49.87" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{06C68CE5-F9F3-46D3-97DC-8969C057FDE5}">
-    <text xml:space="preserve">Enter the day name in the column, or leave it blank if not applicable </text>
-  </threadedComment>
-  <threadedComment ref="N2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{96EB2AF4-8857-453C-84CF-C7D0294A47E1}">
-    <text>End of Month</text>
-  </threadedComment>
-  <threadedComment ref="P2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{ED936B87-B4EA-49D2-9847-251F065AD106}">
-    <text>End of Month</text>
-  </threadedComment>
-  <threadedComment ref="R2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{861CEFFE-75F3-4A22-A7B0-DE08527FCA28}">
-    <text>End of Month</text>
-  </threadedComment>
-  <threadedComment ref="T2" dT="2026-09-14T09:01:47.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{41A77145-9368-44AE-B73E-F2FA9D9BF935}">
-    <text>End of Month</text>
-  </threadedComment>
-  <threadedComment ref="U2" dT="2026-02-27T23:55:36.90" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{73102409-9A79-496E-AAB6-27215C458146}">
-    <text>You can Enter any Time Shift name here</text>
-  </threadedComment>
-  <threadedComment ref="W2" dT="2026-02-27T23:59:32.14" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{C3B48641-F285-4034-95EA-970F81F494AD}">
-    <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </text>
-  </threadedComment>
-  <threadedComment ref="Y2" dT="2026-02-28T00:02:04.50" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{A1D30F49-4CC7-4810-8930-31A0E5E3D18D}">
-    <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. </text>
-  </threadedComment>
-  <threadedComment ref="Z2" dT="2026-02-28T00:02:10.16" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{0D448524-4E4F-4A1C-9A6D-66C1E154C2FC}">
-    <text xml:space="preserve">Use the same time format shown here. For example, enter 08:00:00 for 8:00 AM and 17:00:00 for 5:00 PM. If the time crosses into the next day, prefix it with 1. before the time. For instance, 1.01:00:00 represents 1:00 AM on the following day. 
-</text>
-  </threadedComment>
-  <threadedComment ref="AB2" dT="2026-02-28T00:09:02.95" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{B19BC939-9062-41D8-A080-1F0317F4D29D}">
-    <text xml:space="preserve">This field represents the total working minutes in a day, excluding unpaid breaks. For example, 480 minutes correspond to 8 hours. If an employee is on a compressed schedule, such as 9 hours per day, you must enter the calculation (9 × 60 = 540) to reflect the correct total. </text>
-  </threadedComment>
-  <threadedComment ref="AD2" dT="2026-02-28T00:29:11.91" personId="{178AE33B-3851-45CE-B93D-1C219421A458}" id="{F0E96506-AAF2-49B7-AD58-D5B640AC0623}">
-    <text xml:space="preserve">The Salary Type column defines how an employee’s salary is calculated for the payroll period. It determines whether the computation is based on actual work hours or on a fixed monthly rate.
-Daily and Monthly Variable: Salary is computed based on the employee’s recorded work hours. This means pay is directly tied to attendance and the number of hours worked within the period.
-Monthly Fixed: Salary is calculated based on the employee’s fixed monthly rate. Deductions are applied for lateness, undertime (UT), and absences, but the base salary remains constant regardless of daily work hours.
-By specifying the correct salary type, the system ensures accurate payroll processing and compliance with company policies
-</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38D9F31A-E2EC-4988-BBA0-8862FC76D1CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AJ6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.7109375" customWidth="1"/>
-    <col min="23" max="23" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="8.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.85546875" customWidth="1"/>
-    <col min="32" max="32" width="15.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14.5666666666667" customWidth="1"/>
+    <col min="2" max="2" width="12.1416666666667" customWidth="1"/>
+    <col min="3" max="3" width="10.1416666666667" customWidth="1"/>
+    <col min="4" max="4" width="12.2833333333333" customWidth="1"/>
+    <col min="5" max="5" width="9.85833333333333" customWidth="1"/>
+    <col min="6" max="6" width="5.70833333333333" customWidth="1"/>
+    <col min="7" max="7" width="7.28333333333333" customWidth="1"/>
+    <col min="8" max="9" width="9.85833333333333" customWidth="1"/>
+    <col min="10" max="10" width="17.2833333333333" customWidth="1"/>
+    <col min="11" max="11" width="11.7083333333333" customWidth="1"/>
+    <col min="12" max="12" width="13.1416666666667" customWidth="1"/>
+    <col min="13" max="13" width="8.14166666666667" customWidth="1"/>
+    <col min="14" max="14" width="6" customWidth="1"/>
+    <col min="15" max="15" width="8.14166666666667" customWidth="1"/>
+    <col min="16" max="16" width="6" customWidth="1"/>
+    <col min="17" max="17" width="8.14166666666667" customWidth="1"/>
+    <col min="18" max="18" width="6" customWidth="1"/>
+    <col min="19" max="19" width="8.14166666666667" customWidth="1"/>
+    <col min="20" max="20" width="6" customWidth="1"/>
+    <col min="21" max="21" width="20.8583333333333" customWidth="1"/>
+    <col min="22" max="22" width="11.7083333333333" customWidth="1"/>
+    <col min="23" max="23" width="9.85833333333333" style="1" customWidth="1"/>
+    <col min="24" max="26" width="8.14166666666667" style="1" customWidth="1"/>
+    <col min="27" max="27" width="14.2833333333333" style="2" customWidth="1"/>
+    <col min="28" max="28" width="20" style="3" customWidth="1"/>
+    <col min="29" max="29" width="15.425" customWidth="1"/>
+    <col min="30" max="31" width="18.8583333333333" customWidth="1"/>
+    <col min="32" max="32" width="15.2833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
+    <row r="1" ht="39" customHeight="1" spans="1:36">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="5"/>
+      <c r="T1" s="5"/>
+      <c r="U1" s="5"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="5"/>
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5"/>
+      <c r="Z1" s="5"/>
+      <c r="AA1" s="5"/>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
       <c r="E2" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>18</v>
+      </c>
+      <c r="R2" t="s">
+        <v>19</v>
+      </c>
+      <c r="S2" t="s">
+        <v>20</v>
+      </c>
+      <c r="T2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" t="s">
+        <v>23</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH2" t="s">
         <v>35</v>
       </c>
-      <c r="N2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="AI2" t="s">
         <v>36</v>
       </c>
-      <c r="P2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="AJ2" t="s">
         <v>37</v>
       </c>
-      <c r="R2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" t="s">
-        <v>44</v>
-      </c>
-      <c r="U2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V2" t="s">
-        <v>14</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>29</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>32</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>46</v>
-      </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -968,39 +1586,39 @@
         <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="V3" t="s">
-        <v>24</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X3" s="1">
+        <v>42</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" s="6">
         <v>0.5</v>
       </c>
-      <c r="Y3" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="Z3" s="1">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="AA3" s="4">
+      <c r="Y3" s="6">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="Z3" s="6">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="AA3" s="2">
         <v>60</v>
       </c>
-      <c r="AB3" s="4">
+      <c r="AB3" s="2">
         <v>480</v>
       </c>
       <c r="AC3" t="b">
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36">
       <c r="L4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1021,9 +1639,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36">
       <c r="L5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -1050,9 +1668,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36">
       <c r="L6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M6">
         <v>31</v>
@@ -1066,6 +1684,7 @@
     <mergeCell ref="B1:AC1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hrms-api/wwwroot/Templates/employee_template.xlsx
+++ b/hrms-api/wwwroot/Templates/employee_template.xlsx
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>Instructions:</t>
   </si>
@@ -348,6 +348,9 @@
     <t>SalaryType</t>
   </si>
   <si>
+    <t>Monthly Rate</t>
+  </si>
+  <si>
     <t>Daily Rate</t>
   </si>
   <si>
@@ -363,7 +366,28 @@
     <t>HDMF</t>
   </si>
   <si>
+    <t>TIN</t>
+  </si>
+  <si>
     <t>Email</t>
+  </si>
+  <si>
+    <t>Date Birth</t>
+  </si>
+  <si>
+    <t>Contact Number</t>
+  </si>
+  <si>
+    <t>Civil Status</t>
+  </si>
+  <si>
+    <t>Blood Type</t>
+  </si>
+  <si>
+    <t>Address 1</t>
+  </si>
+  <si>
+    <t>Address 2</t>
   </si>
   <si>
     <t>Saturday</t>
@@ -403,7 +427,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,13 +438,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -878,148 +895,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1374,8 +1391,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AJ6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:AR6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="14.5666666666667" customWidth="1"/>
     <col min="2" max="2" width="12.1416666666667" customWidth="1"/>
@@ -1403,11 +1420,13 @@
     <col min="27" max="27" width="14.2833333333333" style="2" customWidth="1"/>
     <col min="28" max="28" width="20" style="3" customWidth="1"/>
     <col min="29" max="29" width="15.425" customWidth="1"/>
-    <col min="30" max="31" width="18.8583333333333" customWidth="1"/>
-    <col min="32" max="32" width="15.2833333333333" customWidth="1"/>
+    <col min="30" max="32" width="18.8583333333333" customWidth="1"/>
+    <col min="33" max="33" width="15.2833333333333" customWidth="1"/>
+    <col min="39" max="39" width="11.875" customWidth="1"/>
+    <col min="40" max="40" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39" customHeight="1" spans="1:36">
+    <row r="1" ht="39" customHeight="1" spans="1:44">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1443,8 +1462,9 @@
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
+      <c r="AF1" s="5"/>
     </row>
-    <row r="2" spans="1:36">
+    <row r="2" spans="1:44">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1553,19 +1573,43 @@
       <c r="AJ2" t="s">
         <v>37</v>
       </c>
+      <c r="AK2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="3" spans="1:36">
+    <row r="3" spans="1:44">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L3" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -1586,13 +1630,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="V3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="X3" s="6">
         <v>0.5</v>
@@ -1613,12 +1657,12 @@
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:36">
+    <row r="4" spans="1:44">
       <c r="L4" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1639,9 +1683,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:36">
+    <row r="5" spans="1:44">
       <c r="L5" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -1668,9 +1712,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36">
+    <row r="6" spans="1:44">
       <c r="L6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M6">
         <v>31</v>

--- a/hrms-api/wwwroot/Templates/employee_template.xlsx
+++ b/hrms-api/wwwroot/Templates/employee_template.xlsx
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>Instructions:</t>
   </si>
@@ -388,6 +388,12 @@
   </si>
   <si>
     <t>Address 2</t>
+  </si>
+  <si>
+    <t>Project Site</t>
+  </si>
+  <si>
+    <t>Cash Bond</t>
   </si>
   <si>
     <t>Saturday</t>
@@ -1391,7 +1397,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AR6"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="1" max="1" width="14.5666666666667" customWidth="1"/>
@@ -1424,9 +1430,11 @@
     <col min="33" max="33" width="15.2833333333333" customWidth="1"/>
     <col min="39" max="39" width="11.875" customWidth="1"/>
     <col min="40" max="40" width="17.625" customWidth="1"/>
+    <col min="45" max="45" width="11.375" customWidth="1"/>
+    <col min="46" max="46" width="13.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39" customHeight="1" spans="1:44">
+    <row r="1" ht="39" customHeight="1" spans="1:46">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1464,7 +1472,7 @@
       <c r="AE1" s="5"/>
       <c r="AF1" s="5"/>
     </row>
-    <row r="2" spans="1:44">
+    <row r="2" spans="1:46">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1597,19 +1605,25 @@
       <c r="AR2" t="s">
         <v>45</v>
       </c>
+      <c r="AS2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="3" spans="1:44">
+    <row r="3" spans="1:46">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -1630,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="U3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X3" s="6">
         <v>0.5</v>
@@ -1657,12 +1671,12 @@
         <v>1</v>
       </c>
       <c r="AD3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:44">
+    <row r="4" spans="1:46">
       <c r="L4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -1683,9 +1697,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:44">
+    <row r="5" spans="1:46">
       <c r="L5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="M5">
         <v>7</v>
@@ -1712,9 +1726,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:44">
+    <row r="6" spans="1:46">
       <c r="L6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M6">
         <v>31</v>
